--- a/outputs/daily/hr_rankings_2026-10-14_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-14_full.xlsx
@@ -760,12 +760,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>56</v>
+        <v>58.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel</t>
+          <t>Elite Power, Strong Barrel</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -808,10 +808,10 @@
         <v>38.7</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S2" t="n">
-        <v>81.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T2" t="n">
         <v>50</v>
@@ -821,39 +821,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -996,8 +992,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -1011,12 +1015,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>669257</t>
+          <t>606192</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Will Smith</t>
+          <t>Teoscar Hernández</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1036,12 +1040,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1060,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>55</v>
+        <v>54.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1074,62 +1078,58 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>51.1</v>
+        <v>45.7</v>
       </c>
       <c r="Q3" t="n">
         <v>38.7</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S3" t="n">
-        <v>90.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T3" t="n">
         <v>78</v>
       </c>
       <c r="U3" t="n">
-        <v>100</v>
+        <v>48.3</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1149,22 +1149,22 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Contact streak: 8/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1174,72 +1174,72 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>10.94</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>45.19</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>89.76</t>
+          <t>90.27</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>100.2559</t>
+          <t>101.5782</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.5002</t>
+          <t>0.4427</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.2249</t>
+          <t>0.1878</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.3857</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>69.84</t>
+          <t>72.62</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>30.74</t>
+          <t>34.92</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.1765</t>
+          <t>0.1727</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
@@ -1272,8 +1272,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -1287,12 +1295,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>606192</t>
+          <t>669257</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Teoscar Hernandez</t>
+          <t>Will Smith</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1312,12 +1320,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1336,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>50.8</v>
+        <v>54.4</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1350,62 +1358,58 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>45.7</v>
+        <v>51.1</v>
       </c>
       <c r="Q4" t="n">
         <v>38.7</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S4" t="n">
-        <v>92.09999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="T4" t="n">
         <v>78</v>
       </c>
       <c r="U4" t="n">
-        <v>48.3</v>
+        <v>100</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1425,22 +1429,22 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Contact streak: 8/25 over last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1450,72 +1454,72 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>90.27</t>
+          <t>89.76</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>101.5782</t>
+          <t>100.2559</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.4427</t>
+          <t>0.5002</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.1878</t>
+          <t>0.2249</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.3857</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>72.62</t>
+          <t>69.84</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>26.95</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>34.92</t>
+          <t>30.74</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.1727</t>
+          <t>0.1765</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1548,8 +1552,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -1563,12 +1575,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>605141</t>
+          <t>681624</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Andy Pages</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1588,12 +1600,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1612,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>45.1</v>
+        <v>50.9</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1626,62 +1638,58 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>32.7</v>
+        <v>36.4</v>
       </c>
       <c r="Q5" t="n">
         <v>38.7</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S5" t="n">
-        <v>88.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>78</v>
       </c>
       <c r="U5" t="n">
-        <v>29.2</v>
+        <v>66</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1701,22 +1709,22 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1731,67 +1739,67 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>40.77</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>89.87</t>
+          <t>88.81</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>98.5265</t>
+          <t>99.6965</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.4311</t>
+          <t>0.4378</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.1567</t>
+          <t>0.1686</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3363</t>
+          <t>0.3349</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>69.46</t>
+          <t>72.85</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>38.53</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>33.31</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.1823</t>
+          <t>0.1925</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1824,8 +1832,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -1839,12 +1855,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>518692</t>
+          <t>605141</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1864,12 +1880,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1888,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>44.9</v>
+        <v>48.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1902,62 +1918,58 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>39.3</v>
+        <v>32.7</v>
       </c>
       <c r="Q6" t="n">
         <v>38.7</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S6" t="n">
-        <v>95.5</v>
+        <v>93.2</v>
       </c>
       <c r="T6" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U6" t="n">
-        <v>13</v>
+        <v>29.2</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1977,27 +1989,27 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/29, 0 HR</t>
+          <t>Last 7 games: 5/26, 1 HR</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -2007,67 +2019,67 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>42.62</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>89.92</t>
+          <t>89.87</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>100.1411</t>
+          <t>98.5265</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4642</t>
+          <t>0.4311</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1811</t>
+          <t>0.1567</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3591</t>
+          <t>0.3363</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>70.01</t>
+          <t>69.46</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>7.77</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>26.93</t>
+          <t>33.31</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1615</t>
+          <t>0.1823</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -2100,8 +2112,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -2115,12 +2135,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>681624</t>
+          <t>518692</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Andy Pages</t>
+          <t>Freddie Freeman</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2140,12 +2160,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -2164,7 +2184,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>44.1</v>
+        <v>48.6</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2178,62 +2198,58 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>36.4</v>
+        <v>39.3</v>
       </c>
       <c r="Q7" t="n">
         <v>38.7</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S7" t="n">
-        <v>59.8</v>
+        <v>100</v>
       </c>
       <c r="T7" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U7" t="n">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2258,22 +2274,22 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/29, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -2283,67 +2299,67 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.79</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>40.77</t>
+          <t>42.62</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>88.81</t>
+          <t>89.92</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>99.6965</t>
+          <t>100.1411</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4378</t>
+          <t>0.4642</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1686</t>
+          <t>0.1811</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3349</t>
+          <t>0.3591</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>72.85</t>
+          <t>70.01</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>7.77</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>38.53</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1925</t>
+          <t>0.1615</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -2376,8 +2392,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -2416,7 +2440,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2440,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>43.5</v>
+        <v>47.2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2454,7 +2478,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -2464,10 +2488,10 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S8" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T8" t="n">
         <v>78</v>
@@ -2477,39 +2501,35 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2652,8 +2672,16 @@
           <t>22.73</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -2667,24 +2695,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>641343</t>
+          <t>663656</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jake Bauers</t>
+          <t>Kyle Tucker</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-10-15T00:00:00Z</t>
@@ -2692,22 +2720,22 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Blake Snell</t>
+          <t>Robert Gasser</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>605483</t>
+          <t>688107</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -2716,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>40.8</v>
+        <v>46.1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2730,62 +2758,58 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>59.6</v>
+        <v>33.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>38.7</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S9" t="n">
-        <v>81.90000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T9" t="n">
         <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>16.6</v>
+        <v>12</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2805,12 +2829,12 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -2820,12 +2844,12 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -2835,101 +2859,109 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>13.91</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>50.01</t>
+          <t>37.53</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>91.98</t>
+          <t>88.98</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>102.9654</t>
+          <t>98.7109</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.464</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.2167</t>
+          <t>0.1598</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3659</t>
+          <t>0.3433</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>71.58</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>69.02</t>
+          <t>20.59</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>42.96</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.2018</t>
+          <t>0.1658</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>21.26</t>
+          <t>37.12</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>83.89</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.2559</t>
+          <t>0.3953</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.0609</t>
+          <t>0.1607</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>22.73</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+          <t>25.77</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -2943,24 +2975,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>663656</t>
+          <t>641343</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kyle Tucker</t>
+          <t>Jake Bauers</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-10-15T00:00:00Z</t>
@@ -2968,22 +3000,22 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Robert Gasser</t>
+          <t>Blake Snell</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>688107</t>
+          <t>605483</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -2992,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>39.8</v>
+        <v>44.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3006,62 +3038,58 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>33.9</v>
+        <v>59.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>38.7</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S10" t="n">
-        <v>71.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T10" t="n">
         <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>12</v>
+        <v>16.6</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3081,12 +3109,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -3096,12 +3124,12 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 6/26, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -3111,101 +3139,109 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>13.91</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>37.53</t>
+          <t>50.01</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>88.98</t>
+          <t>91.98</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>98.7109</t>
+          <t>102.9654</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.464</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1598</t>
+          <t>0.2167</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3433</t>
+          <t>0.3659</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>71.58</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>69.02</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>42.96</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1658</t>
+          <t>0.2018</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>37.12</t>
+          <t>21.26</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>83.89</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.3953</t>
+          <t>0.2559</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.1607</t>
+          <t>0.0609</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>25.77</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+          <t>22.73</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -3244,7 +3280,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3268,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>39.2</v>
+        <v>42.9</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3282,7 +3318,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -3292,10 +3328,10 @@
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S11" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T11" t="n">
         <v>78</v>
@@ -3305,39 +3341,35 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3480,8 +3512,16 @@
           <t>22.73</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -3495,12 +3535,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>596142</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Gary Sanchez</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3520,12 +3560,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -3544,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>38.2</v>
+        <v>41.3</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3558,62 +3598,58 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>38.4</v>
+        <v>36.6</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S12" t="n">
-        <v>90.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="T12" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U12" t="n">
-        <v>28.9</v>
+        <v>65.2</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3633,27 +3669,27 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -3663,67 +3699,67 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>9.15</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>42.05</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>89.52</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>100.6173</t>
+          <t>100.4264</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.4042</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.1782</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3297</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>71.85</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>25.54</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>46.82</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.2052</t>
+          <t>0.1715</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
@@ -3756,8 +3792,16 @@
           <t>22.73</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -3771,12 +3815,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>683734</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Andrew Vaughn</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3796,12 +3840,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3820,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>37.6</v>
+        <v>39.7</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3834,62 +3878,58 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>36.6</v>
+        <v>34.1</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S13" t="n">
-        <v>95.5</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U13" t="n">
-        <v>65.2</v>
+        <v>13.6</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3909,27 +3949,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/19, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -3939,67 +3979,67 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>44.76</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>90.55</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>100.1817</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.4097</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.143</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.335</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>70.46</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>12.66</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>33.72</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>24.97</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1715</t>
+          <t>0.1437</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
@@ -4032,8 +4072,16 @@
           <t>22.73</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -4072,7 +4120,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4096,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>35.2</v>
+        <v>38.9</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4110,7 +4158,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -4120,10 +4168,10 @@
         <v>37.5</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S14" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T14" t="n">
         <v>75</v>
@@ -4133,39 +4181,35 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4308,8 +4352,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -4323,24 +4375,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>500743</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Miguel Rojas</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-15T00:00:00Z</t>
@@ -4348,22 +4400,22 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Robert Gasser</t>
+          <t>Blake Snell</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>688107</t>
+          <t>605483</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -4372,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>33.6</v>
+        <v>38.8</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4386,62 +4438,58 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>17.3</v>
+        <v>47.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>38.7</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>76.2</v>
       </c>
       <c r="T15" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U15" t="n">
-        <v>14.1</v>
+        <v>13.3</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4461,12 +4509,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -4476,116 +4524,124 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/14, 0 HR</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>92.36</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>98.0168</t>
+          <t>103.8477</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3776</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1083</t>
+          <t>0.1589</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3039</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>68.8</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>77.44</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>32.81</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>23.17</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1273</t>
+          <t>0.1342</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>37.12</t>
+          <t>21.26</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>83.89</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.3953</t>
+          <t>0.2559</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.1607</t>
+          <t>0.0609</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>25.77</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+          <t>22.73</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -4599,24 +4655,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>500743</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Miguel Rojas</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-15T00:00:00Z</t>
@@ -4624,7 +4680,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4634,12 +4690,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Blake Snell</t>
+          <t>Robert Gasser</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>605483</t>
+          <t>688107</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -4648,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>31.8</v>
+        <v>37.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4662,62 +4718,58 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>47.1</v>
+        <v>17.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>38.7</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T16" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U16" t="n">
-        <v>13.3</v>
+        <v>14.1</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4737,12 +4789,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -4752,116 +4804,124 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Last 7 games: 3/14, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>103.8477</t>
+          <t>98.0168</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.3776</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.1083</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3039</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>68.8</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>77.44</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>23.17</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1342</t>
+          <t>0.1273</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>21.26</t>
+          <t>37.12</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>83.89</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.2559</t>
+          <t>0.3953</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.0609</t>
+          <t>0.1607</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>22.73</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+          <t>25.77</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -4875,12 +4935,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>800325</t>
+          <t>806198</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4900,12 +4960,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -4924,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>26.9</v>
+        <v>28.2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4938,62 +4998,58 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>16.6</v>
+        <v>10.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S17" t="n">
-        <v>71.7</v>
+        <v>64.3</v>
       </c>
       <c r="T17" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U17" t="n">
-        <v>5.1</v>
+        <v>24.9</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -5013,12 +5069,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -5028,12 +5084,12 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -5043,67 +5099,67 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>98.8409</t>
+          <t>96.5693</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>0.087</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -5136,8 +5192,16 @@
           <t>22.73</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -5151,12 +5215,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>806198</t>
+          <t>687401</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>Joey Ortiz</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5176,12 +5240,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -5200,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>24.5</v>
+        <v>27.5</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5214,65 +5278,61 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>10.5</v>
+        <v>17.1</v>
       </c>
       <c r="Q18" t="n">
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>44.8</v>
       </c>
       <c r="T18" t="n">
         <v>78</v>
       </c>
       <c r="U18" t="n">
-        <v>24.9</v>
+        <v>22.4</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -5289,12 +5349,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -5304,7 +5364,7 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 7/26, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -5319,67 +5379,67 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>36.16</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.91</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>96.5693</t>
+          <t>99.2209</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3403</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.2904</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>30.57</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>31.91</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>19.68</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>0.1185</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
@@ -5412,8 +5472,16 @@
           <t>22.73</t>
         </is>
       </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -5427,12 +5495,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>687401</t>
+          <t>800325</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Joey Ortiz</t>
+          <t>Luis Lara</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -5452,12 +5520,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -5476,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>23.8</v>
+        <v>27.3</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5490,65 +5558,61 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>17.1</v>
+        <v>16.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T19" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U19" t="n">
-        <v>22.4</v>
+        <v>5.1</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr"/>
@@ -5565,7 +5629,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
@@ -5580,12 +5644,12 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 0 HR</t>
+          <t>Last 7 games: 4/26, 0 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -5595,67 +5659,67 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>36.16</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>87.91</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>99.2209</t>
+          <t>98.8409</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.3403</t>
+          <t>0.331</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.075</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.2904</t>
+          <t>0.293</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>31.91</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>19.68</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.1185</t>
+          <t>0.079</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
@@ -5688,8 +5752,16 @@
           <t>22.73</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -6054,12 +6126,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -6078,7 +6150,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>56</v>
+        <v>58.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6092,7 +6164,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel</t>
+          <t>Elite Power, Strong Barrel</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -6102,10 +6174,10 @@
         <v>38.7</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S2" t="n">
-        <v>81.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T2" t="n">
         <v>50</v>
@@ -6115,39 +6187,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6290,8 +6358,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -6305,12 +6381,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>669257</t>
+          <t>606192</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Will Smith</t>
+          <t>Teoscar Hernández</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -6330,12 +6406,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -6354,7 +6430,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>55</v>
+        <v>54.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6368,62 +6444,58 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>51.1</v>
+        <v>45.7</v>
       </c>
       <c r="Q3" t="n">
         <v>38.7</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S3" t="n">
-        <v>90.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T3" t="n">
         <v>78</v>
       </c>
       <c r="U3" t="n">
-        <v>100</v>
+        <v>48.3</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6443,22 +6515,22 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Contact streak: 8/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -6468,72 +6540,72 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>10.94</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>45.19</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>89.76</t>
+          <t>90.27</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>100.2559</t>
+          <t>101.5782</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.5002</t>
+          <t>0.4427</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.2249</t>
+          <t>0.1878</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.3857</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>69.84</t>
+          <t>72.62</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>30.74</t>
+          <t>34.92</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.1765</t>
+          <t>0.1727</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
@@ -6566,8 +6638,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -6581,12 +6661,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>606192</t>
+          <t>669257</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Teoscar Hernandez</t>
+          <t>Will Smith</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -6606,12 +6686,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -6630,7 +6710,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>50.8</v>
+        <v>54.4</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6644,62 +6724,58 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>45.7</v>
+        <v>51.1</v>
       </c>
       <c r="Q4" t="n">
         <v>38.7</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S4" t="n">
-        <v>92.09999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="T4" t="n">
         <v>78</v>
       </c>
       <c r="U4" t="n">
-        <v>48.3</v>
+        <v>100</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6719,22 +6795,22 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Contact streak: 8/25 over last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -6744,72 +6820,72 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>90.27</t>
+          <t>89.76</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>101.5782</t>
+          <t>100.2559</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.4427</t>
+          <t>0.5002</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.1878</t>
+          <t>0.2249</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.3857</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>72.62</t>
+          <t>69.84</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>26.95</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>34.92</t>
+          <t>30.74</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.1727</t>
+          <t>0.1765</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -6842,8 +6918,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -6857,12 +6941,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>605141</t>
+          <t>681624</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Andy Pages</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -6882,12 +6966,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -6906,7 +6990,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>45.1</v>
+        <v>50.9</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -6920,62 +7004,58 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>32.7</v>
+        <v>36.4</v>
       </c>
       <c r="Q5" t="n">
         <v>38.7</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S5" t="n">
-        <v>88.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>78</v>
       </c>
       <c r="U5" t="n">
-        <v>29.2</v>
+        <v>66</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6995,22 +7075,22 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -7025,67 +7105,67 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>40.77</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>89.87</t>
+          <t>88.81</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>98.5265</t>
+          <t>99.6965</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.4311</t>
+          <t>0.4378</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.1567</t>
+          <t>0.1686</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3363</t>
+          <t>0.3349</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>69.46</t>
+          <t>72.85</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>38.53</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>33.31</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.1823</t>
+          <t>0.1925</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -7118,8 +7198,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -7133,12 +7221,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>518692</t>
+          <t>605141</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -7158,12 +7246,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -7182,7 +7270,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>44.9</v>
+        <v>48.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7196,62 +7284,58 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>39.3</v>
+        <v>32.7</v>
       </c>
       <c r="Q6" t="n">
         <v>38.7</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S6" t="n">
-        <v>95.5</v>
+        <v>93.2</v>
       </c>
       <c r="T6" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U6" t="n">
-        <v>13</v>
+        <v>29.2</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7271,27 +7355,27 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/29, 0 HR</t>
+          <t>Last 7 games: 5/26, 1 HR</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -7301,67 +7385,67 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>42.62</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>89.92</t>
+          <t>89.87</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>100.1411</t>
+          <t>98.5265</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4642</t>
+          <t>0.4311</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1811</t>
+          <t>0.1567</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3591</t>
+          <t>0.3363</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>70.01</t>
+          <t>69.46</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>7.77</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>26.93</t>
+          <t>33.31</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1615</t>
+          <t>0.1823</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -7394,8 +7478,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -7409,12 +7501,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>681624</t>
+          <t>518692</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Andy Pages</t>
+          <t>Freddie Freeman</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -7434,12 +7526,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -7458,7 +7550,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>44.1</v>
+        <v>48.6</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7472,62 +7564,58 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>36.4</v>
+        <v>39.3</v>
       </c>
       <c r="Q7" t="n">
         <v>38.7</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S7" t="n">
-        <v>59.8</v>
+        <v>100</v>
       </c>
       <c r="T7" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U7" t="n">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7552,22 +7640,22 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/29, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -7577,67 +7665,67 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.79</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>40.77</t>
+          <t>42.62</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>88.81</t>
+          <t>89.92</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>99.6965</t>
+          <t>100.1411</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4378</t>
+          <t>0.4642</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1686</t>
+          <t>0.1811</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3349</t>
+          <t>0.3591</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>72.85</t>
+          <t>70.01</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>7.77</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>38.53</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1925</t>
+          <t>0.1615</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -7670,8 +7758,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -7710,7 +7806,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -7734,7 +7830,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>43.5</v>
+        <v>47.2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7748,7 +7844,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -7758,10 +7854,10 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S8" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T8" t="n">
         <v>78</v>
@@ -7771,39 +7867,35 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7946,8 +8038,16 @@
           <t>22.73</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -7961,24 +8061,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>641343</t>
+          <t>663656</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jake Bauers</t>
+          <t>Kyle Tucker</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-10-15T00:00:00Z</t>
@@ -7986,22 +8086,22 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Blake Snell</t>
+          <t>Robert Gasser</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>605483</t>
+          <t>688107</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -8010,7 +8110,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>40.8</v>
+        <v>46.1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8024,62 +8124,58 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>59.6</v>
+        <v>33.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>38.7</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S9" t="n">
-        <v>81.90000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T9" t="n">
         <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>16.6</v>
+        <v>12</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8099,12 +8195,12 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -8114,12 +8210,12 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -8129,101 +8225,109 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>13.91</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>50.01</t>
+          <t>37.53</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>91.98</t>
+          <t>88.98</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>102.9654</t>
+          <t>98.7109</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.464</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.2167</t>
+          <t>0.1598</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3659</t>
+          <t>0.3433</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>71.58</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>69.02</t>
+          <t>20.59</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>42.96</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.2018</t>
+          <t>0.1658</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>21.26</t>
+          <t>37.12</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>83.89</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.2559</t>
+          <t>0.3953</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.0609</t>
+          <t>0.1607</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>22.73</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+          <t>25.77</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -8237,24 +8341,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>663656</t>
+          <t>641343</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kyle Tucker</t>
+          <t>Jake Bauers</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-10-15T00:00:00Z</t>
@@ -8262,22 +8366,22 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Robert Gasser</t>
+          <t>Blake Snell</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>688107</t>
+          <t>605483</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -8286,7 +8390,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>39.8</v>
+        <v>44.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8300,62 +8404,58 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>33.9</v>
+        <v>59.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>38.7</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S10" t="n">
-        <v>71.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T10" t="n">
         <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>12</v>
+        <v>16.6</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8375,12 +8475,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -8390,12 +8490,12 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 6/26, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -8405,101 +8505,109 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>13.91</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>37.53</t>
+          <t>50.01</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>88.98</t>
+          <t>91.98</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>98.7109</t>
+          <t>102.9654</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.464</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1598</t>
+          <t>0.2167</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3433</t>
+          <t>0.3659</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>71.58</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>69.02</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>42.96</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1658</t>
+          <t>0.2018</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>37.12</t>
+          <t>21.26</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>83.89</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.3953</t>
+          <t>0.2559</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.1607</t>
+          <t>0.0609</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>25.77</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+          <t>22.73</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -8538,7 +8646,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -8562,7 +8670,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>39.2</v>
+        <v>42.9</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8576,7 +8684,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -8586,10 +8694,10 @@
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S11" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T11" t="n">
         <v>78</v>
@@ -8599,39 +8707,35 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8774,8 +8878,16 @@
           <t>22.73</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -8789,12 +8901,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>596142</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Gary Sanchez</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -8814,12 +8926,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -8838,7 +8950,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>38.2</v>
+        <v>41.3</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8852,62 +8964,58 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>38.4</v>
+        <v>36.6</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S12" t="n">
-        <v>90.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="T12" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U12" t="n">
-        <v>28.9</v>
+        <v>65.2</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8927,27 +9035,27 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -8957,67 +9065,67 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>9.15</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>42.05</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>89.52</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>100.6173</t>
+          <t>100.4264</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.4042</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.1782</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3297</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>71.85</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>25.54</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>46.82</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.2052</t>
+          <t>0.1715</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
@@ -9050,8 +9158,16 @@
           <t>22.73</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -9065,12 +9181,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>683734</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Andrew Vaughn</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -9090,12 +9206,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -9114,7 +9230,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>37.6</v>
+        <v>39.7</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9128,62 +9244,58 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>36.6</v>
+        <v>34.1</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S13" t="n">
-        <v>95.5</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U13" t="n">
-        <v>65.2</v>
+        <v>13.6</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9203,27 +9315,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/19, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -9233,67 +9345,67 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>44.76</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>90.55</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>100.1817</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.4097</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.143</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.335</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>70.46</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>12.66</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>33.72</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>24.97</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1715</t>
+          <t>0.1437</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
@@ -9326,8 +9438,16 @@
           <t>22.73</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -9366,7 +9486,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -9390,7 +9510,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>35.2</v>
+        <v>38.9</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9404,7 +9524,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -9414,10 +9534,10 @@
         <v>37.5</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S14" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T14" t="n">
         <v>75</v>
@@ -9427,39 +9547,35 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9602,8 +9718,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -9617,24 +9741,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>500743</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Miguel Rojas</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-15T00:00:00Z</t>
@@ -9642,22 +9766,22 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Robert Gasser</t>
+          <t>Blake Snell</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>688107</t>
+          <t>605483</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -9666,7 +9790,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>33.6</v>
+        <v>38.8</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9680,62 +9804,58 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>17.3</v>
+        <v>47.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>38.7</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>76.2</v>
       </c>
       <c r="T15" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U15" t="n">
-        <v>14.1</v>
+        <v>13.3</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9755,12 +9875,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -9770,116 +9890,124 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/14, 0 HR</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>92.36</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>98.0168</t>
+          <t>103.8477</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3776</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1083</t>
+          <t>0.1589</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3039</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>68.8</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>77.44</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>32.81</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>23.17</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1273</t>
+          <t>0.1342</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>37.12</t>
+          <t>21.26</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>83.89</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.3953</t>
+          <t>0.2559</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.1607</t>
+          <t>0.0609</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>25.77</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+          <t>22.73</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -9893,24 +10021,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>500743</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Miguel Rojas</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-15T00:00:00Z</t>
@@ -9918,7 +10046,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -9928,12 +10056,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Blake Snell</t>
+          <t>Robert Gasser</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>605483</t>
+          <t>688107</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -9942,7 +10070,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>31.8</v>
+        <v>37.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -9956,62 +10084,58 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>47.1</v>
+        <v>17.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>38.7</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T16" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U16" t="n">
-        <v>13.3</v>
+        <v>14.1</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10031,12 +10155,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -10046,116 +10170,124 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Last 7 games: 3/14, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>103.8477</t>
+          <t>98.0168</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.3776</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.1083</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3039</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>68.8</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>77.44</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>23.17</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1342</t>
+          <t>0.1273</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>21.26</t>
+          <t>37.12</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>83.89</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.2559</t>
+          <t>0.3953</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.0609</t>
+          <t>0.1607</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>22.73</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+          <t>25.77</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -10169,12 +10301,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>800325</t>
+          <t>806198</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -10194,12 +10326,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -10218,7 +10350,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>26.9</v>
+        <v>28.2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10232,62 +10364,58 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>16.6</v>
+        <v>10.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S17" t="n">
-        <v>71.7</v>
+        <v>64.3</v>
       </c>
       <c r="T17" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U17" t="n">
-        <v>5.1</v>
+        <v>24.9</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -10307,12 +10435,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -10322,12 +10450,12 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -10337,67 +10465,67 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>98.8409</t>
+          <t>96.5693</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>0.087</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -10430,8 +10558,16 @@
           <t>22.73</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -10445,12 +10581,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>806198</t>
+          <t>687401</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>Joey Ortiz</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -10470,12 +10606,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -10494,7 +10630,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>24.5</v>
+        <v>27.5</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10508,65 +10644,61 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>10.5</v>
+        <v>17.1</v>
       </c>
       <c r="Q18" t="n">
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>44.8</v>
       </c>
       <c r="T18" t="n">
         <v>78</v>
       </c>
       <c r="U18" t="n">
-        <v>24.9</v>
+        <v>22.4</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -10583,12 +10715,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -10598,7 +10730,7 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 7/26, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -10613,67 +10745,67 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>36.16</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.91</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>96.5693</t>
+          <t>99.2209</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3403</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.2904</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>30.57</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>31.91</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>19.68</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>0.1185</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
@@ -10706,8 +10838,16 @@
           <t>22.73</t>
         </is>
       </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -10721,12 +10861,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>687401</t>
+          <t>800325</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Joey Ortiz</t>
+          <t>Luis Lara</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -10746,12 +10886,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -10770,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>23.8</v>
+        <v>27.3</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10784,65 +10924,61 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>17.1</v>
+        <v>16.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T19" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U19" t="n">
-        <v>22.4</v>
+        <v>5.1</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr"/>
@@ -10859,7 +10995,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
@@ -10874,12 +11010,12 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 0 HR</t>
+          <t>Last 7 games: 4/26, 0 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 3.1% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -10889,67 +11025,67 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>36.16</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>87.91</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>99.2209</t>
+          <t>98.8409</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.3403</t>
+          <t>0.331</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.075</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.2904</t>
+          <t>0.293</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>31.91</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>19.68</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.1185</t>
+          <t>0.079</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
@@ -10982,8 +11118,16 @@
           <t>22.73</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
